--- a/literature/LLM_Geospatial_Chatbot_LitReview.xlsx
+++ b/literature/LLM_Geospatial_Chatbot_LitReview.xlsx
@@ -8,42 +8,50 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Esraa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877C5E0A-1DF9-4D2C-A2B0-6D0E73B90CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDCC8BF0-DF60-484E-9920-2E7CE1CBD461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Papers" sheetId="1" r:id="rId1"/>
+    <sheet name="GitHub Links " sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
+  <si>
+    <t>NO.</t>
+  </si>
   <si>
     <t>Paper Title</t>
   </si>
   <si>
+    <t>Link</t>
+  </si>
+  <si>
     <t>Year</t>
   </si>
   <si>
     <t>Journal / Conference</t>
-  </si>
-  <si>
-    <t>Main Contribution</t>
-  </si>
-  <si>
-    <t>Use Case / Application</t>
-  </si>
-  <si>
-    <t>Limitations / Gaps</t>
-  </si>
-  <si>
-    <t>Link</t>
-  </si>
-  <si>
-    <t>NO.</t>
   </si>
   <si>
     <r>
@@ -109,17 +117,186 @@
       <t>(How LLM or chatbot is combined with geospatial data (e.g., APIs, embedding)</t>
     </r>
   </si>
+  <si>
+    <t>Main Contribution</t>
+  </si>
+  <si>
+    <t>Use Case / Application</t>
+  </si>
+  <si>
+    <t>Limitations / Gaps</t>
+  </si>
+  <si>
+    <t>BB-GeoGPT: A framework for learning a large language model for geographic information science</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0306457324001675?casa_token=AwpsjLGsIDAAAAAA:B3gQluzTlUrQMmAcSyVpJ5B0bJsLochpfNK1jcUuXLdxbAM_q2ltlX1dAIj9jmSvsdJlsOn0tFXD</t>
+  </si>
+  <si>
+    <t>Journal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OmniGeo: Towards a Multimodal Large Language Models for Geospatial Artificial Intelligence
+</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2503.16326</t>
+  </si>
+  <si>
+    <t>Preprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GeoLLM: Extracting Geospatial Knowledge from Large Language Models
+</t>
+  </si>
+  <si>
+    <t>https://openreview.net/forum?id=TqL2xBwXP3</t>
+  </si>
+  <si>
+    <t>Conference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An autonomous GIS agent framework for geospatial data retrieval
+</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/doi/full/10.1080/17538947.2025.2458688</t>
+  </si>
+  <si>
+    <t>Text-to-OverpassQL: A Natural Language Interface for Complex
+Geodata Querying of OpenStreetMap</t>
+  </si>
+  <si>
+    <t>https://direct.mit.edu/tacl/article/doi/10.1162/tacl_a_00654/120832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GeoGPT: Understanding and Processing Geospatial Tasks through An Autonomous GPT
+</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2307.07930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geospatial large language model trained with a simulated environment for generating tool-use chains autonomously
+</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S1569843224006708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGeoAI: Enabling Geospatial Analysis for Public through Natural Language, with Large Language Models
+</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/2220-9964/13/10/348#:~:text=Large%20Language%20Models%20,ontology%20mapping%2C%20the%20framework%20accurately</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GeoTool-GPT: a trainable method for facilitating Large Language Models to master GIS tools
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(maybe no access)</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/doi/full/10.1080/13658816.2024.2438937</t>
+  </si>
+  <si>
+    <t>GeoAgent: To Empower LLMs using Geospatial Tools for Address Standardization</t>
+  </si>
+  <si>
+    <t>https://aclanthology.org/2024.findings-acl.362/</t>
+  </si>
+  <si>
+    <t>Are Large Language Models Geospatially Knowledgeable?</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/abs/10.1145/3589132.3625625</t>
+  </si>
+  <si>
+    <t>ACM-Conference</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Fine-Tuning LLM-Assisted Chinese Disaster Geospatial Intelligence Extraction and Case Studies
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(no access)</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.proquest.com/scholarly-journals/fine-tuning-llm-assisted-chinese-disaster/docview/3171009986/se-2?accountid=42604</t>
+  </si>
+  <si>
+    <t>ISPRS International Journal of Geo-Information</t>
+  </si>
+  <si>
+    <t>Is ChatGPT a Good Geospatial Data Analyst? Exploring the Integration of Natural Language into Structured Query Language within a Spatial Database</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/2220-9964/13/1/26</t>
+  </si>
+  <si>
+    <t>Geode: A Zero-shot Geospatial Question-Answering Agent with Explicit Reasoning and Precise Spatio-Temporal Retrieval</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2407.11014</t>
+  </si>
+  <si>
+    <t>arXiv</t>
+  </si>
+  <si>
+    <t>GeoQAMap - Geographic Question Answering with Maps Leveraging LLM and Open Knowledge Base</t>
+  </si>
+  <si>
+    <t>https://drops.dagstuhl.de/entities/document/10.4230/LIPIcs.GIScience.2023.28</t>
+  </si>
+  <si>
+    <t>Seems interesting paper</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -135,6 +312,26 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -176,22 +373,34 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -494,87 +703,595 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" customWidth="1"/>
+    <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" customWidth="1"/>
     <col min="4" max="4" width="16.5546875" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="31.88671875" customWidth="1"/>
-    <col min="7" max="7" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="31.6640625" customWidth="1"/>
     <col min="8" max="8" width="29.44140625" customWidth="1"/>
     <col min="9" max="9" width="32.33203125" customWidth="1"/>
-    <col min="10" max="10" width="29.77734375" customWidth="1"/>
+    <col min="10" max="10" width="29.6640625" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="90" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>2024</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>2025</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>2024</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5" spans="1:12" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>2025</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="52.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
+      <c r="B6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>2024</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>2023</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>2025</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9">
+        <v>2024</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10">
+        <v>2024</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12">
+        <v>2023</v>
+      </c>
+      <c r="E12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13">
+        <v>2025</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14">
+        <v>2024</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15">
+        <v>2024</v>
+      </c>
+      <c r="E15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16">
+        <v>2023</v>
+      </c>
+      <c r="E16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="4"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{F325B474-9865-469E-9767-80E74A4687F6}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{4090E6EA-0871-4000-9B86-A416A6D88236}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{51AC1853-4082-4984-AF14-F1533CFD2892}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{E3C19B2B-E3C0-4DCD-98D9-F65D782B9F52}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{9A3D01FE-EAEF-42E5-A90D-1B268BF66628}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{30201377-77C2-4E64-BD91-B9CBF7CEEFDD}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{DC3F8956-5CEF-41DA-BBEC-2DD0E2B5BDE3}"/>
+    <hyperlink ref="C9" r:id="rId8" location=":~:text=Large%20Language%20Models%20,ontology%20mapping%2C%20the%20framework%20accurately" xr:uid="{2E6664AE-DFD9-4BAE-BFFD-461DA5CB5B16}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{B98EEFE1-8348-4330-992F-EB9C6846EC81}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{836C3D57-D3DE-42AA-9797-3AE35A865C4A}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{5981C73B-6A0A-4B53-9412-5EB730050D52}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{FDEF6920-8160-433D-8912-B69A86CBF5E0}"/>
+    <hyperlink ref="E13" r:id="rId13" xr:uid="{F57AC6DC-3DA2-44B5-A7C1-E2753B7CFD2F}"/>
+    <hyperlink ref="E14" r:id="rId14" xr:uid="{87A74733-FB23-474B-A186-21DB3385283A}"/>
+    <hyperlink ref="C14" r:id="rId15" xr:uid="{74295F4A-8EF4-45E3-A8A2-EF1D06491BF0}"/>
+    <hyperlink ref="C15" r:id="rId16" xr:uid="{231E6076-196A-48EA-A6FA-ADC70427294C}"/>
+    <hyperlink ref="C16" r:id="rId17" xr:uid="{E64DCDFC-1D6E-417F-AA49-6B993E8E4F61}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA89B46-7F48-4406-84A1-9B5503C6EE4E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="e872c03a-cd30-432a-9c67-9b05f4eb8449" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100052BC163AFD8AB47AA9F475712D68F55" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cd632a81ef04c82d13bed11b116750ee">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="e872c03a-cd30-432a-9c67-9b05f4eb8449" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="63a20cf217351dc492b594fe63c43b1e" ns3:_="">
+    <xsd:import namespace="e872c03a-cd30-432a-9c67-9b05f4eb8449"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e872c03a-cd30-432a-9c67-9b05f4eb8449" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="13" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="17" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3464B1BD-1719-4B0F-B29A-A46DA0D6FCEB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e872c03a-cd30-432a-9c67-9b05f4eb8449"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A57CADC7-A9CA-4165-AF12-9C574E4C29D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e872c03a-cd30-432a-9c67-9b05f4eb8449"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77DD8AD3-1009-4926-A6C9-DD27640F0A68}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{e0ba2eba-5425-4d9b-b24b-f0f4845bcf62}" enabled="0" method="" siteId="{e0ba2eba-5425-4d9b-b24b-f0f4845bcf62}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/literature/LLM_Geospatial_Chatbot_LitReview.xlsx
+++ b/literature/LLM_Geospatial_Chatbot_LitReview.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Esraa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDCC8BF0-DF60-484E-9920-2E7CE1CBD461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91756E42-75FA-4CCB-B06D-CE673053A69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="139">
   <si>
     <t>NO.</t>
   </si>
@@ -278,7 +278,369 @@
     <t>https://drops.dagstuhl.de/entities/document/10.4230/LIPIcs.GIScience.2023.28</t>
   </si>
   <si>
-    <t>Seems interesting paper</t>
+    <t>LLaMA-2-7B model, adapted via domain-specific pretraining and supervised fine-tuning (instruction tuning).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	GIS-specific textual corpus including academic GIS papers, Wikipedia pages related to geographical technology, and annotated geospatial datasets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	GIS knowledge analyst: Responding to geospatial queries, extracting geospatial information, and understanding domain-specific geographic terms and questions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	LLM (LLaMA-2-7B) fine-tuned with GIS-specific corpus through two-stage training: (1) domain-specific pretraining on GIS textual data, (2) supervised instruction-tuning with professional GIS instructions (Self-Instruct approach, Rule-based approach, and annotated professional geospatial datasets).</t>
+  </si>
+  <si>
+    <t>Developed BB-GeoGPT, a GIS-specialized LLM with improved performance in geospatial question-answering, spatial relation extraction, geospatial summarization, and geospatial text generation, significantly outperforming general-domain LLMs of similar size.</t>
+  </si>
+  <si>
+    <t>GIS domain-specific tasks including geospatial queries, geospatial information extraction, location/entity recognition, spatial relation extraction, geospatial text summarization, and domain-specific Q&amp;A in Geographic Information Science.</t>
+  </si>
+  <si>
+    <t>* Performance gap remains compared to commercial large models (GPT-3.5/GPT-4), especially in terms of completeness and detailed response generation.
+* Limited by current corpus size and quality; identified need for larger and higher-quality training datasets specifically in spatial analysis, geodatabases, and remote sensing.
+- Challenges with deployment due to computational resource requirements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Multimodal LLM (OmniGeo), based on LLaVA1.5 and Qwen2-VL models, fine-tuned using multimodal instruction datasets through LoRA (Low-Rank Adaptation) and full-supervision fine-tuning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Satellite imagery (RS images), street-view images, geospatial vector data (points of interest - POIs, spatial polygons, and geographic entities), textual geographic data (tweets, webpages, captions generated by image captioning models).</t>
+  </si>
+  <si>
+    <t>Multi-domain geospatial assistant capable of urban perception prediction, remote sensing image classification, urban geography (region function classification), health geography (forecasting), and geospatial semantics (location description and toponym recognition).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multimodal integration using instruction fine-tuning:Geographic spatial data (vectors, POIs) converted to textual paragraphs.
+Images (RS and street view) converted into captions via image-captioning models (InstructBLIP).
+Aligned geographic entities combined into multimodal instructions for fine-tuning OmniGeo via LoRA and full fine-tuning methods. </t>
+  </si>
+  <si>
+    <t>OmniGeo is the first large-scale multimodal LLM specifically designed for GeoAI, successfully integrating diverse data modalities (text, images, spatial data) to perform multiple geospatial tasks simultaneously, achieving state-of-the-art performance, comparable or superior to models like GPT-4o on multimodal geospatial tasks.</t>
+  </si>
+  <si>
+    <t>Dementia death counts forecasting (Health Geography).
+Urban functional region classification (Urban Geography).
+Remote sensing image scene classification.
+Urban perception prediction (e.g., assessing noise, beauty, liveliness).
+Geospatial semantics (location extraction and toponym recognition).</t>
+  </si>
+  <si>
+    <t>Complexity in handling extensive and varied geospatial multimodal data may introduce inference noise.
+Performance variations observed across tasks, indicating further optimization potential.
+Resource-intensive deployment due to extensive multimodal data and model complexity.
+Challenges remain in the spatial reasoning grounded in real-world geospatial contexts.</t>
+  </si>
+  <si>
+    <t>GPT-3.5 (primary), LLaMA-2, RoBERTa; fine-tuned models leveraging supervised fine-tuning with specific prompt structures (address and nearby places from OpenStreetMap)</t>
+  </si>
+  <si>
+    <t>Geographic coordinates (latitude, longitude), OpenStreetMap data (address descriptions, names of nearby places, directions, and distances)</t>
+  </si>
+  <si>
+    <t>Geospatial predictor: Answers queries related to population density, economic indicators (asset wealth, income, home value), health-related indicators, education levels, and geospatial attributes based on location coordinates.</t>
+  </si>
+  <si>
+    <t>Integration through specialized prompts including geographic coordinates, reverse-geocoded addresses, and nearby place information from OpenStreetMap; fine-tuned with constructed prompts to extract detailed spatial knowledge from LLM embeddings.</t>
+  </si>
+  <si>
+    <t>Introduced GeoLLM, a method significantly enhancing the extraction of geospatial information from LLMs by effectively fine-tuning models using map-based auxiliary prompts, improving prediction performance for geospatial tasks by up to 70% compared to traditional baselines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	- Population density estimation globally.
+- Economic and socioeconomic indicators (asset wealth, income, home values).
+- Educational attainment and health indicators.
+- General geospatial data querying and analysis tasks.</t>
+  </si>
+  <si>
+    <t>Dependency on quality of map data (e.g., OpenStreetMap data quality varies globally).
+- Challenges in numeric coordinate interpretation by LLMs.
+- Limited effectiveness in remote or less-known areas without detailed contextual descriptions.
+- Computational intensity of fine-tuning and inference.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	GPT-4o (OpenAI), utilized as a reasoning core to autonomously select data sources, interpret user queries, and generate Python scripts for geospatial data retrieval.</t>
+  </si>
+  <si>
+    <t>Administrative boundaries, demographic data, satellite imagery, digital elevation models (DEM), weather data, COVID-19 data, and spatial vector datasets from sources including OpenStreetMap, US Census Bureau, ESRI World Imagery, OpenTopography, and commercial weather data providers.</t>
+  </si>
+  <si>
+    <t>Autonomous GIS agent that autonomously retrieves geospatial data by interpreting natural language requests, selecting appropriate data sources, and executing generated code to obtain data without manual intervention.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	- Uses LLM (GPT-4o) as a decision-making core for selecting the appropriate data source and generating Python scripts.
+- Incorporates a plug-and-play framework consisting of data source indices and detailed handbooks for each data source.
+- Python scripts generated by LLM are executed in GIS software (QGIS plugin) and Python environments.</t>
+  </si>
+  <si>
+    <t>Developed the LLM-Find framework, one of the first universal, autonomous GIS agent frameworks for retrieving geospatial data. It autonomously selects data sources and retrieves data using natural language instructions, significantly reducing human intervention. Demonstrated through extensive tests across multiple GIS data sources.</t>
+  </si>
+  <si>
+    <t>*Autonomous retrieval of spatial data for urban planning, emergency management, public health monitoring (e.g., COVID-19 tracking), demographic studies, environmental monitoring, and geographic analyses.
+*Integrated into QGIS as a plugin for direct use by GIS analysts and developers, and as an interactive Python application for advanced GIS tasks.</t>
+  </si>
+  <si>
+    <t>*Currently limited to predefined textual handbooks, insufficient for complex or multimodal data sources.
+- Constraints related to prompt length limitations of LLMs.
+- Dependency on manual creation of handbooks.
+- Limited capability in assessing data suitability, quality, and spatial context autonomously.
+- Potential issues with code accuracy due to LLM limitations.</t>
+  </si>
+  <si>
+    <t>GPT-4 (OpenAI), fine-tuned sequence-to-sequence models (T5-based models: CodeT5, ByT5), with in-context learning methods (retrieval-based few-shot prompting using sentence-BERT embeddings).</t>
+  </si>
+  <si>
+    <t>OpenStreetMap database, including spatial elements like nodes, ways, and relations tagged with key-value pairs; geographic coordinates, points of interest, roads, buildings, natural features, and administrative boundaries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Natural language geospatial query translator: Converts complex user requests in natural language into executable OverpassQL queries for accessing specific geospatial data from OpenStreetMap.</t>
+  </si>
+  <si>
+    <t>*NLP models translate natural language input into OverpassQL queries directly.
+- Queries are executed against the OpenStreetMap database through the Overpass API.
+- Few-shot in-context examples retrieved by semantic similarity (sentence-BERT embeddings) are used with GPT-4 to guide accurate query generation.</t>
+  </si>
+  <si>
+    <t>Proposed the first large-scale, real-world dataset (OverpassNL) of 8,352 natural language queries paired with complex OverpassQL queries for geodata retrieval. Developed task-specific metrics to evaluate generated queries and executed outputs. Demonstrated the effectiveness of fine-tuned sequence models and large language models (especially GPT-4) for natural language geodata query translation.</t>
+  </si>
+  <si>
+    <t>*Empower novice users to perform complex geospatial queries without prior knowledge of OverpassQL.
+- Help experienced GIS users quickly draft and refine queries, reducing manual effort.
+- Facilitate large language models in retrieving precise geospatial data for various applications such as geodata analysis, urban planning, humanitarian mapping, and location-based services.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	*Model-generated queries can introduce syntax errors, limiting immediate applicability.
+- Dependency on the quality and comprehensiveness of OpenStreetMap data.
+- Challenges in correctly interpreting ambiguities and inconsistencies within user-generated tags and data annotations.
+- Resource-intensive deployment, particularly when using advanced LLMs like GPT-4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	GPT-3.5-turbo (OpenAI) integrated through LangChain framework; used for semantic understanding, autonomous reasoning, and decision-making to select and execute GIS tools.</t>
+  </si>
+  <si>
+    <t>Points of Interest (POI), road networks, remote sensing images (satellite imagery), spatial vector datasets (e.g., shapefiles), geographic coordinates (latitude, longitude), spatial polygons.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Autonomous GIS assistant capable of interpreting user-provided natural language instructions to autonomously perform geospatial data collection, spatial data processing, analysis (e.g., facility siting, spatial queries), and visualization (mapping tasks).</t>
+  </si>
+  <si>
+    <t>*Uses LangChain framework to connect GPT-3.5-turbo LLM with predefined GIS tools.
+- LLM autonomously selects and calls GIS tools (Buffer, Intersect, Erase, Clip, Land Use Classification, Raster-to-Vector, etc.) based on semantic reasoning from natural language instructions.
+- Operates iteratively (Think-Plan-Act loop) until geospatial tasks are completed successfully.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Introduced GeoGPT, an autonomous framework integrating LLM (GPT-3.5-turbo) with traditional and specialized GIS tools via the LangChain framework. It significantly reduces the complexity and barrier for non-expert users by autonomously translating natural language queries into accurate and executable GIS workflows, effectively solving diverse geospatial tasks without manual intervention.</t>
+  </si>
+  <si>
+    <t>*Autonomous geospatial data crawling (POIs, road networks, remote sensing images).
+- Spatial queries and facility siting (e.g., site selection for schools and hotels).
+- Geospatial data visualization and thematic mapping (land-use classification).
+- General geospatial data processing and analysis tasks in urban planning, environmental management, public health, and related GIS-based applications.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	*Uncertainty and inconsistency in outputs due to LLM variability.
+- Potential confusion arising from ambiguous natural language terms and multiple semantic meanings.
+- Dependency on predefined GIS tools limits flexibility and adaptability to highly complex or novel tasks.
+- Challenges with accuracy and reliability in tool selection, particularly under conditions of ambiguous or insufficiently detailed user requests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	LLaMA-2-7B (open-source LLM), fine-tuned using instruction tuning with seed task-guided self-instruct strategy.</t>
+  </si>
+  <si>
+    <t>GIS vector datasets (point, line, polygon shapefiles), raster data, remote sensing imagery.</t>
+  </si>
+  <si>
+    <t>Autonomous GIS task solver: Generates and executes tool-use chains to autonomously solve geospatial tasks (e.g., site selection, data extraction, spatial analysis).</t>
+  </si>
+  <si>
+    <t>*Fine-tuning LLaMA-2-7B using self-instruct-generated instruction tuning data.
+- Employing simulated environments to mimic geospatial tool execution and generate corresponding tool-use chains autonomously.
+- Uses a structured workflow (framework-workflow) approach to clarify tool selection and data streams.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Developed GTChain, a geospatial LLM fine-tuned with a simulated environment to autonomously generate accurate tool-use chains for geospatial tasks. Introduced a seed task-guided self-instruct strategy for efficient instruction-tuning data collection. GTChain significantly outperformed GPT-4 and Gemini 1.5 Pro in solving geospatial tasks, demonstrating superior performance on complex tasks requiring multi-step, multi-tool operations.</t>
+  </si>
+  <si>
+    <t>Geospatial data analysis and spatial decision support (e.g., urban planning, environmental monitoring, emergency response).
+- Automating complex GIS workflows involving multiple geospatial analysis tools.
+- Facilitating novice users in executing advanced geospatial analyses without extensive GIS knowledge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Dependency on simulated tool execution limits validation against real-world tool behavior.
+- Potential inaccuracies or hallucinations by LLM during tool-use chain generation.
+- The complexity of real-world geospatial scenarios might not be fully captured by the simulated training environment.
+- Model performance sensitive to input anomalies, although still robust compared to baseline LLMs.</t>
+  </si>
+  <si>
+    <t>Llama 2 (fine-tuned), NLP techniques including tailored Named Entity Recognition (NER) and ontology mapping.</t>
+  </si>
+  <si>
+    <t>GIS datasets including vector and raster formats, geographic features (points, lines, polygons), OpenStreetMap (OSM) data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Provides non-expert users the capability to perform geospatial analyses via natural language queries. Generates executable PyQGIS scripts to automate geospatial tasks and visualize results on maps.</t>
+  </si>
+  <si>
+    <t>Uses NLP (SpaCy library) to preprocess queries, identify entities, and map them to geospatial ontologies (WorldKG).
+- Fine-tuned Llama 2 generates PyQGIS scripts based on enriched natural language inputs.
+- Integrates with QGIS via PyQGIS scripts for executing geospatial analysis and visualization tasks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Developed ChatGeoAI, a novel framework integrating fine-tuned LLM (Llama 2) with NLP and geospatial ontology mapping, enabling automatic translation of natural language queries into executable PyQGIS scripts. Offers a highly accessible GIS interface suitable for non-experts, significantly democratizing geospatial technology and simplifying complex geospatial analyses.</t>
+  </si>
+  <si>
+    <t>*Urban planning, environmental conservation, emergency response, everyday spatial decisions (e.g., facility siting, route planning).
+- Allows intuitive interaction with GIS through natural language, automating complex analysis tasks, spatial querying, routing, and recommendations (e.g., finding nearby facilities, shortest paths, best locations based on multiple criteria).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	*Occasional inaccuracies due to ambiguous attributes and alias terms in natural language queries.
+- Limited handling of exceptional cases or less-structured data inputs.
+- Potential issues with semantic ambiguity in complex queries requiring precise entity interpretation and execution order accuracy.</t>
+  </si>
+  <si>
+    <t>ChatGLM-6B (fine-tuned with LoRA), transformer-based Geocoding model, rule-based NLP for extracting spatial descriptive elements (e.g., directional offsets, colloquial descriptions).</t>
+  </si>
+  <si>
+    <t>GIS data including POI databases, road network data from OpenStreetMap, geographic coordinates, and S2 tokens (Google’s spatial indexing).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Address standardization agent: autonomously standardizes non-standard addresses, handling irregularities such as missing elements, spelling errors, directional offsets, and colloquial descriptions.</t>
+  </si>
+  <si>
+    <t>*Combines ChatGLM-6B fine-tuned LLM with dedicated geospatial tools through API calls.
+- Uses external POI databases, Geocoding models, and offset calculation tools for spatial data processing.
+- Workflow involves LLM-driven task planning, followed by spatial analysis through integrated geospatial tools, and finalized by text standardization leveraging external databases and reverse geocoding APIs.</t>
+  </si>
+  <si>
+    <t>Introduced GeoAgent, a novel framework integrating LLM with geospatial tools, capable of robustly handling and standardizing complex non-standard addresses. Constructed a comprehensive non-standard address dataset and proposed GeoRouge, a new metric specifically designed for address standardization evaluation. Significantly improved performance in address standardization, geocoding accuracy, address linking, and matching tasks compared to traditional methods and baseline models.</t>
+  </si>
+  <si>
+    <t>*Navigation apps, ride-hailing, food delivery, logistics services.
+- Address standardization, geocoding, address linking, address matching tasks.
+- Automating and enhancing accuracy in processing user-input address data across various platforms, significantly improving spatial data quality for downstream applications.</t>
+  </si>
+  <si>
+    <t>*Primarily tested with Chinese addresses; might require adjustments for other languages.
+- Dependent on ChatGLM-6B model, which has limitations in following complex instructions without fine-tuning.
+- Multi-stage framework susceptible to cascading errors (e.g., inaccuracies in initial geocoding could affect subsequent address standardization steps).
+- Requires careful management and regular updates of external POI databases and spatial tools to maintain high accuracy over time, especially due to dynamic real-world address changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	LLaMA (7B and 13B), Alpaca (7B), OPT (6.7B and 13B); tested in both zero-shot and few-shot prompting settings. Focused on geospatial coordinate prediction, spatial preposition interpretation, and reasoning via multidimensional scaling (MDS).</t>
+  </si>
+  <si>
+    <t>City coordinates (latitude/longitude), named city locations in textual format, geographic relational phrases (e.g., "near", "close to", "far from").</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Evaluation agent: Assesses LLMs’ inherent ability to perform geospatial knowledge tasks including city coordinate prediction, interpretation of spatial relationships, and spatial reasoning without explicit external geospatial tools.</t>
+  </si>
+  <si>
+    <t>No explicit integration with external tools or APIs. Instead, geospatial tasks are embedded into prompts and evaluated based on the LLM’s ability to respond with spatially meaningful outputs. Geospatial reasoning simulated using MDS with predicted distances.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	First systematic evaluation of pretrained LLMs' geospatial capabilities. Designed benchmark experiments to assess LLMs’ performance on (1) geospatial knowledge (coordinate prediction), (2) geospatial awareness (understanding of spatial prepositions), and (3) geospatial reasoning (layout prediction using dissimilarity measures and MDS). Demonstrated meaningful spatial understanding in large LLMs.</t>
+  </si>
+  <si>
+    <t>*Evaluating the use of LLMs for answering location-related queries, such as "Where is City X?"
+- Supporting geospatial reasoning tasks like estimating relative city positions or travel distances.
+- Informing future development of LLM-based spatial assistants or agents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	LLMs perform inconsistently depending on model architecture and prompt structure.
+- Spatial predictions are approximate and unsuitable for high-precision geospatial tasks.
+- Lack of real-world tool integration limits practical applications.
+- Ambiguity arises when city names are not accompanied by disambiguating information like state or country names.</t>
+  </si>
+  <si>
+    <t>ChatGPT-4; integrated via prompt engineering with explicit database schema and sample data; includes training with SQL schema (“CREATE TABLE” commands) and in-context learning.</t>
+  </si>
+  <si>
+    <t>Spatial database (PostGIS) containing shapefiles: census blocks, neighborhoods, streets, subway stations, and socioeconomic attributes; uses geometry columns (e.g., geom) for spatial analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Natural language-to-SQL generator: Translates user queries into SQL for spatial databases, performs geospatial analysis (e.g., spatial joins, area calculation, coordinate-based logic), and returns human-readable responses.</t>
+  </si>
+  <si>
+    <t>*Prompts include table schemas and example data.
+- User questions are mapped to SQL queries using ChatGPT.
+- SQL is executed on PostGIS; results are parsed back into human-readable answers by the LLM.
+- Implemented using the LangChain framework for structured prompt management.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Developed a framework for interacting with geospatial databases using ChatGPT. Demonstrated that ChatGPT can generate valid spatial SQL queries and interpret spatial relationships (e.g., using ST_Area, ST_Intersects, ST_Contains). Introduced a benchmark evaluating accuracy across non-spatial, single-table spatial, and multi-table spatial join queries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	*Spatial data exploration through natural language (e.g., population of NYC, neighborhood areas).
+- Geospatial analysis including spatial joins (e.g., subway stations in neighborhoods), area calculations, and proximity-based queries.
+- Potential assistant tool for novice users interacting with spatial databases without SQL knowledge.</t>
+  </si>
+  <si>
+    <t>*Susceptible to hallucinations (e.g., fabricating column names).
+- Assumes spatial units and CRS without confirmation.
+- Order errors in function parameters (e.g., reversed ST_Contains).
+- Accuracy declines with query complexity.
+- Not a replacement for expert analysts, but useful as a geospatial SQL drafting assistant.</t>
+  </si>
+  <si>
+    <t>GPT-3.5, Claude-3 Opus, WizardCoder (local); uses code generation via prompt templates and structured expert APIs; integrates chain-of-thought and tree-of-thought prompting.</t>
+  </si>
+  <si>
+    <t>Satellite imagery, meteorological data (temperature, humidity, precipitation), GIS data (vector and raster), elevation, air quality indices, GeoJSON, real-time weather data.</t>
+  </si>
+  <si>
+    <t>Geospatial QA agent: interprets natural language queries, retrieves spatio-temporal data in real time, and generates textual responses along with map visualizations and Python-executable code for geospatial reasoning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	*Modular architecture with expert APIs (geocoding, air quality, elevation, temperature, etc.)
+- Query translated into code by LLM using provided API specs
+- Code executed in a secure backend (Flask), results returned as textual response and map overlay (via Folium/OpenStreetMap)
+- GeoPatch is used as a standardized geospatial object to structure all vector/raster data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Introduced Geode, a novel zero-shot geospatial QA agent that integrates real-time spatio-temporal data retrieval, reasoning, and multimodal expert systems. Built a reusable architecture for geospatial reasoning using LLM-driven code generation combined with explicit expert APIs and interactive map-based outputs. Demonstrates significantly improved performance in answering complex, time-sensitive geospatial queries compared to standard LLMs.</t>
+  </si>
+  <si>
+    <t>*Environmental monitoring (air quality, weather, elevation, flooding)
+- Urban planning and land use decisions
+- Geospatial analytics for research and public policy
+- Interactive learning and exploration tools using maps and text
+- Real-time querying for disaster management, traffic, pollution analysis, etc.</t>
+  </si>
+  <si>
+    <t>*High dependency on the quality and availability of real-time APIs
+- Potential latency issues with large queries due to complex expert chaining
+- Scalability issues as data modalities increase
+- Requires technical coordination between LLM-generated code and expert APIs to avoid failure
+- Visual or textual explanation quality may degrade for ambiguous or poorly framed queries</t>
+  </si>
+  <si>
+    <t>GPT-3.5 (via OpenAI API); used with prompt engineering, Named Entity Recognition (NER), and SPARQL query generation; entity IDs retrieved via Wikidata API.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Wikidata RDF data including geo-entities with spatial attributes (e.g., coordinates, administrative regions), population figures, time of inception; linked to geographic entities like cities, universities, churches, etc.; GeoSPARQL-compatible data structure.</t>
+  </si>
+  <si>
+    <t>Geospatial QA assistant: interprets natural language questions, converts them into SPARQL queries, retrieves structured geographic data from Wikidata, and visualizes results as interactive maps.</t>
+  </si>
+  <si>
+    <t>*Prompts optimized and parsed to extract named entities and map to Wikidata IDs.
+- SPARQL queries generated using GPT-3.5.
+- Executed via Wikidata SPARQL endpoint.
+- Returned results visualized using folium (in Python) inside Jupyter/Colab environments.
+- Includes manual user input option to refine incomplete or inaccurate outputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Developed GeoQAMap, an end-to-end QA system that bridges natural language, LLMs, SPARQL querying, and interactive map visualization. Demonstrates effective handling of complex questions like conditional filtering, historical comparison, and entity relationships through zero-shot QA enhanced by LLM guidance and knowledge graph querying.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	*Answering questions like “cities in Germany with population &gt; 500,000” or “UK universities over 100 years old.”
+- Supports educational use, public planning, and geographic data exploration.
+- Potential to expand toward geo-analytical QA through integration with additional spatial datasets like OpenStreetMap and CityGML.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	*LLM may produce syntactically invalid SPARQL queries.
+- Wikidata inconsistencies or missing entity mappings can cause query failure.
+- Manual corrections may be needed for complex or ambiguous queries.
+- Currently limited to query-based QA without buffer/spatial operations, though future integration with GeoSPARQL and Ontop is discussed.</t>
   </si>
 </sst>
 </file>
@@ -377,26 +739,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -703,63 +1070,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="31.88671875" customWidth="1"/>
-    <col min="7" max="7" width="31.6640625" customWidth="1"/>
-    <col min="8" max="8" width="29.44140625" customWidth="1"/>
-    <col min="9" max="9" width="32.33203125" customWidth="1"/>
-    <col min="10" max="10" width="29.6640625" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="31" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="8"/>
+    <col min="2" max="2" width="36.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="25" style="4" customWidth="1"/>
+    <col min="6" max="6" width="31.88671875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="39.44140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="41.21875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="42.44140625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="42.109375" style="4" customWidth="1"/>
+    <col min="11" max="11" width="42.6640625" style="4" customWidth="1"/>
+    <col min="12" max="12" width="62.109375" style="4" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="72" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -768,15 +1136,36 @@
       <c r="C2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="4">
         <v>2024</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="F2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+    <row r="3" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -785,32 +1174,74 @@
       <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="4">
         <v>2025</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+    <row r="4" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4">
         <v>2024</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="F4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+    <row r="5" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -819,15 +1250,36 @@
       <c r="C5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4">
         <v>2025</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="F5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" ht="52.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+    <row r="6" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -836,15 +1288,36 @@
       <c r="C6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="4">
         <v>2024</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="F6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+    <row r="7" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -853,15 +1326,36 @@
       <c r="C7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="4">
         <v>2023</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="F7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+    <row r="8" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -870,15 +1364,36 @@
       <c r="C8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="4">
         <v>2025</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="F8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>96</v>
+      </c>
     </row>
-    <row r="9" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+    <row r="9" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -887,134 +1402,254 @@
       <c r="C9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="4">
         <v>2024</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="F9" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
-    <row r="10" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+    <row r="10" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2024</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2023</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2023</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D10">
+      <c r="D15" s="4">
         <v>2024</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E15" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12">
-        <v>2023</v>
-      </c>
-      <c r="E12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7" t="s">
+    <row r="16" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D13">
+      <c r="D16" s="4">
         <v>2025</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E16" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14">
-        <v>2024</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15">
-        <v>2024</v>
-      </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16">
-        <v>2023</v>
-      </c>
-      <c r="E16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1026,15 +1661,15 @@
     <hyperlink ref="C7" r:id="rId6" xr:uid="{30201377-77C2-4E64-BD91-B9CBF7CEEFDD}"/>
     <hyperlink ref="C8" r:id="rId7" xr:uid="{DC3F8956-5CEF-41DA-BBEC-2DD0E2B5BDE3}"/>
     <hyperlink ref="C9" r:id="rId8" location=":~:text=Large%20Language%20Models%20,ontology%20mapping%2C%20the%20framework%20accurately" xr:uid="{2E6664AE-DFD9-4BAE-BFFD-461DA5CB5B16}"/>
-    <hyperlink ref="C10" r:id="rId9" xr:uid="{B98EEFE1-8348-4330-992F-EB9C6846EC81}"/>
-    <hyperlink ref="C11" r:id="rId10" xr:uid="{836C3D57-D3DE-42AA-9797-3AE35A865C4A}"/>
-    <hyperlink ref="C12" r:id="rId11" xr:uid="{5981C73B-6A0A-4B53-9412-5EB730050D52}"/>
-    <hyperlink ref="C13" r:id="rId12" xr:uid="{FDEF6920-8160-433D-8912-B69A86CBF5E0}"/>
-    <hyperlink ref="E13" r:id="rId13" xr:uid="{F57AC6DC-3DA2-44B5-A7C1-E2753B7CFD2F}"/>
-    <hyperlink ref="E14" r:id="rId14" xr:uid="{87A74733-FB23-474B-A186-21DB3385283A}"/>
-    <hyperlink ref="C14" r:id="rId15" xr:uid="{74295F4A-8EF4-45E3-A8A2-EF1D06491BF0}"/>
-    <hyperlink ref="C15" r:id="rId16" xr:uid="{231E6076-196A-48EA-A6FA-ADC70427294C}"/>
-    <hyperlink ref="C16" r:id="rId17" xr:uid="{E64DCDFC-1D6E-417F-AA49-6B993E8E4F61}"/>
+    <hyperlink ref="C15" r:id="rId9" xr:uid="{B98EEFE1-8348-4330-992F-EB9C6846EC81}"/>
+    <hyperlink ref="C10" r:id="rId10" xr:uid="{836C3D57-D3DE-42AA-9797-3AE35A865C4A}"/>
+    <hyperlink ref="C11" r:id="rId11" xr:uid="{5981C73B-6A0A-4B53-9412-5EB730050D52}"/>
+    <hyperlink ref="C16" r:id="rId12" xr:uid="{FDEF6920-8160-433D-8912-B69A86CBF5E0}"/>
+    <hyperlink ref="E16" r:id="rId13" xr:uid="{F57AC6DC-3DA2-44B5-A7C1-E2753B7CFD2F}"/>
+    <hyperlink ref="E12" r:id="rId14" xr:uid="{87A74733-FB23-474B-A186-21DB3385283A}"/>
+    <hyperlink ref="C12" r:id="rId15" xr:uid="{74295F4A-8EF4-45E3-A8A2-EF1D06491BF0}"/>
+    <hyperlink ref="C13" r:id="rId16" xr:uid="{231E6076-196A-48EA-A6FA-ADC70427294C}"/>
+    <hyperlink ref="C14" r:id="rId17" xr:uid="{E64DCDFC-1D6E-417F-AA49-6B993E8E4F61}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1251,15 +1886,15 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3464B1BD-1719-4B0F-B29A-A46DA0D6FCEB}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="e872c03a-cd30-432a-9c67-9b05f4eb8449"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="e872c03a-cd30-432a-9c67-9b05f4eb8449"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/literature/LLM_Geospatial_Chatbot_LitReview.xlsx
+++ b/literature/LLM_Geospatial_Chatbot_LitReview.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Esraa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Esraa\Documents\GitHub\fds-project-geollms\literature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91756E42-75FA-4CCB-B06D-CE673053A69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB61E5B0-F6BD-4B84-88DE-30520995E12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,70 +54,6 @@
     <t>Journal / Conference</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">LLM Used / NLP Method
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>( GPT, BERT, fine-tuned model, rule-based NLP, etc. )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Geospatial Data Type 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Coordinates, maps, GIS layers, satellite imagery, etc.)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Chatbot Role 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(What the chatbot does (e.g., tourism guide, emergency assistant, etc.))</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Integration Method 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(How LLM or chatbot is combined with geospatial data (e.g., APIs, embedding)</t>
-    </r>
-  </si>
-  <si>
     <t>Main Contribution</t>
   </si>
   <si>
@@ -191,27 +127,6 @@
     <t>https://www.mdpi.com/2220-9964/13/10/348#:~:text=Large%20Language%20Models%20,ontology%20mapping%2C%20the%20framework%20accurately</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">GeoTool-GPT: a trainable method for facilitating Large Language Models to master GIS tools
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(maybe no access)</t>
-    </r>
-  </si>
-  <si>
     <t>https://www.tandfonline.com/doi/full/10.1080/13658816.2024.2438937</t>
   </si>
   <si>
@@ -230,27 +145,6 @@
     <t>ACM-Conference</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Fine-Tuning LLM-Assisted Chinese Disaster Geospatial Intelligence Extraction and Case Studies
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(no access)</t>
-    </r>
-  </si>
-  <si>
     <t>https://www.proquest.com/scholarly-journals/fine-tuning-llm-assisted-chinese-disaster/docview/3171009986/se-2?accountid=42604</t>
   </si>
   <si>
@@ -276,6 +170,22 @@
   </si>
   <si>
     <t>https://drops.dagstuhl.de/entities/document/10.4230/LIPIcs.GIScience.2023.28</t>
+  </si>
+  <si>
+    <t>LLM Used / NLP Method
+( GPT, BERT, fine-tuned model, rule-based NLP, etc. )</t>
+  </si>
+  <si>
+    <t>Geospatial Data Type 
+(Coordinates, maps, GIS layers, satellite imagery, etc.)</t>
+  </si>
+  <si>
+    <t>Chatbot Role 
+(What the chatbot does (e.g., tourism guide, emergency assistant, etc.))</t>
+  </si>
+  <si>
+    <t>Integration Method 
+(How LLM or chatbot is combined with geospatial data (e.g., APIs, embedding)</t>
   </si>
   <si>
     <t>LLaMA-2-7B model, adapted via domain-specific pretraining and supervised fine-tuning (instruction tuning).</t>
@@ -642,12 +552,20 @@
 - Manual corrections may be needed for complex or ambiguous queries.
 - Currently limited to query-based QA without buffer/spatial operations, though future integration with GeoSPARQL and Ontop is discussed.</t>
   </si>
+  <si>
+    <t>GeoTool-GPT: a trainable method for facilitating Large Language Models to master GIS tools
+(maybe no access)</t>
+  </si>
+  <si>
+    <t>Fine-Tuning LLM-Assisted Chinese Disaster Geospatial Intelligence Extraction and Case Studies
+(no access)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -677,23 +595,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -737,32 +643,29 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1070,32 +973,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="8"/>
-    <col min="2" max="2" width="36.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="25" style="4" customWidth="1"/>
-    <col min="6" max="6" width="31.88671875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="39.44140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="41.21875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="42.44140625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="42.109375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="42.6640625" style="4" customWidth="1"/>
-    <col min="12" max="12" width="62.109375" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="4"/>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="6" max="6" width="31.88671875" customWidth="1"/>
+    <col min="7" max="7" width="31.6640625" customWidth="1"/>
+    <col min="8" max="8" width="29.44140625" customWidth="1"/>
+    <col min="9" max="9" width="32.33203125" customWidth="1"/>
+    <col min="10" max="10" width="29.6640625" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="90" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -1105,572 +1007,571 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="8">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D3" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4">
+      <c r="F3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5">
         <v>2024</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>54</v>
+      <c r="E4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="4">
+    <row r="5" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="5">
         <v>2025</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>61</v>
+      <c r="E5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="7" t="s">
+    <row r="6" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="4">
+      <c r="C6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="5">
         <v>2024</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>68</v>
+      <c r="E6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="7" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D7" s="5">
+        <v>2023</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="5">
         <v>2025</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>75</v>
+      <c r="E8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="4">
+    <row r="9" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="5">
         <v>2024</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>82</v>
+      <c r="E9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="144" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="4">
+    <row r="10" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="5">
         <v>2023</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>89</v>
+      <c r="E11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="144" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2025</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>96</v>
+    <row r="12" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>122</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="4">
+    <row r="13" spans="1:12" ht="216" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="5">
         <v>2024</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>103</v>
+      <c r="E13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="4">
-        <v>2024</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="4">
+    <row r="14" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="5">
         <v>2023</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="4">
-        <v>2024</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="4">
-        <v>2024</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="K13" s="4" t="s">
+      <c r="E14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="G14" s="5" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="4">
-        <v>2023</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="H14" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="I14" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="J14" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="K14" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="L14" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="4">
+      <c r="B15" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="5">
         <v>2024</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="E15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
     </row>
-    <row r="16" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+    <row r="16" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="4">
+      <c r="B16" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="5">
         <v>2025</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="E16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="3"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{F325B474-9865-469E-9767-80E74A4687F6}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{4090E6EA-0871-4000-9B86-A416A6D88236}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{51AC1853-4082-4984-AF14-F1533CFD2892}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{E3C19B2B-E3C0-4DCD-98D9-F65D782B9F52}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{9A3D01FE-EAEF-42E5-A90D-1B268BF66628}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{30201377-77C2-4E64-BD91-B9CBF7CEEFDD}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{DC3F8956-5CEF-41DA-BBEC-2DD0E2B5BDE3}"/>
-    <hyperlink ref="C9" r:id="rId8" location=":~:text=Large%20Language%20Models%20,ontology%20mapping%2C%20the%20framework%20accurately" xr:uid="{2E6664AE-DFD9-4BAE-BFFD-461DA5CB5B16}"/>
-    <hyperlink ref="C15" r:id="rId9" xr:uid="{B98EEFE1-8348-4330-992F-EB9C6846EC81}"/>
-    <hyperlink ref="C10" r:id="rId10" xr:uid="{836C3D57-D3DE-42AA-9797-3AE35A865C4A}"/>
-    <hyperlink ref="C11" r:id="rId11" xr:uid="{5981C73B-6A0A-4B53-9412-5EB730050D52}"/>
-    <hyperlink ref="C16" r:id="rId12" xr:uid="{FDEF6920-8160-433D-8912-B69A86CBF5E0}"/>
-    <hyperlink ref="E16" r:id="rId13" xr:uid="{F57AC6DC-3DA2-44B5-A7C1-E2753B7CFD2F}"/>
-    <hyperlink ref="E12" r:id="rId14" xr:uid="{87A74733-FB23-474B-A186-21DB3385283A}"/>
-    <hyperlink ref="C12" r:id="rId15" xr:uid="{74295F4A-8EF4-45E3-A8A2-EF1D06491BF0}"/>
-    <hyperlink ref="C13" r:id="rId16" xr:uid="{231E6076-196A-48EA-A6FA-ADC70427294C}"/>
-    <hyperlink ref="C14" r:id="rId17" xr:uid="{E64DCDFC-1D6E-417F-AA49-6B993E8E4F61}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1685,14 +1586,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="e872c03a-cd30-432a-9c67-9b05f4eb8449" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100052BC163AFD8AB47AA9F475712D68F55" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cd632a81ef04c82d13bed11b116750ee">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="e872c03a-cd30-432a-9c67-9b05f4eb8449" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="63a20cf217351dc492b594fe63c43b1e" ns3:_="">
     <xsd:import namespace="e872c03a-cd30-432a-9c67-9b05f4eb8449"/>
@@ -1874,6 +1767,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="e872c03a-cd30-432a-9c67-9b05f4eb8449" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1884,22 +1785,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3464B1BD-1719-4B0F-B29A-A46DA0D6FCEB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="e872c03a-cd30-432a-9c67-9b05f4eb8449"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A57CADC7-A9CA-4165-AF12-9C574E4C29D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1917,6 +1802,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3464B1BD-1719-4B0F-B29A-A46DA0D6FCEB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e872c03a-cd30-432a-9c67-9b05f4eb8449"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77DD8AD3-1009-4926-A6C9-DD27640F0A68}">
   <ds:schemaRefs>
